--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79168</v>
+        <v>79184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79184</v>
+        <v>79196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79196</v>
+        <v>79218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79218</v>
+        <v>79222</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79222</v>
+        <v>79228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79235</v>
+        <v>79237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>113407078</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>79265</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,6 +1761,862 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114666740</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493093</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6939985</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114666741</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493078</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6939958</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114666739</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493104</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6939973</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114666736</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>493114</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6940015</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114666738</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>493120</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6939985</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114666733</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492947</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6940165</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114666737</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>493101</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6939990</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114666735</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>493109</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6940063</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack 2 träd</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119869896</v>
+        <v>119869867</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,39 +2631,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2709,12 +2709,18 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119869867</v>
+        <v>119869896</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,39 +2751,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2823,18 +2829,12 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>119869867</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>119869896</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119869867</v>
+        <v>119869896</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,39 +2631,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2709,18 +2709,12 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2739,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119869896</v>
+        <v>119869867</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2751,39 +2745,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,12 +2823,18 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>114666739</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>114666737</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>114666741</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>114666733</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>114666736</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>114666738</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>114666740</v>
       </c>
       <c r="B18" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>114666735</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>114666739</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>114666737</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>114666741</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>114666733</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>114666736</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>114666738</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>114666740</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>114666735</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 32898-2023 artfynd.xlsx
+++ b/artfynd/A 32898-2023 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>114666739</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>114666737</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>114666741</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>114666733</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>114666736</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>114666738</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>114666740</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>114666735</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
